--- a/data/refresh_schedule.xlsx
+++ b/data/refresh_schedule.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B22"/>
+  <dimension ref="A1:B23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -479,7 +479,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Ademar</t>
+          <t>Ademar Cruz</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -515,7 +515,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Cleide</t>
+          <t>Cleide Lima</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -527,7 +527,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Edvaldo</t>
+          <t>Edvaldo Correa</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -563,7 +563,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Gilmara</t>
+          <t>Gilmara Dantas</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -599,7 +599,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Monique</t>
+          <t>Monique Bendahan</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -635,7 +635,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Silvana</t>
+          <t>Silvana Souza</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -675,6 +675,18 @@
         </is>
       </c>
       <c r="B22" t="inlineStr">
+        <is>
+          <t>08:00,18:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Superintendência</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
         <is>
           <t>08:00,18:00</t>
         </is>

--- a/data/refresh_schedule.xlsx
+++ b/data/refresh_schedule.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B23"/>
+  <dimension ref="A1:B22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,18 +680,6 @@
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Superintendência</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>08:00,18:00</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/refresh_schedule.xlsx
+++ b/data/refresh_schedule.xlsx
@@ -413,13 +413,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B22"/>
+  <dimension ref="A1:B25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>lider</t>
+          <t>gestor</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Adamilton Bentes</t>
+          <t>GRI</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -443,7 +443,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Fabiana Cunha</t>
+          <t>PDI</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -455,7 +455,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Jairton Melo</t>
+          <t>PPI</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -467,7 +467,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Jousanete Dias</t>
+          <t>CAI</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -479,7 +479,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Ademar Cruz</t>
+          <t>COM</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -491,7 +491,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Alexandre Barbosa</t>
+          <t>GE</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -503,7 +503,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Alexandre Guimarães</t>
+          <t>LOG</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -515,7 +515,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Cleide Lima</t>
+          <t>PENSA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -527,7 +527,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Edvaldo Correa</t>
+          <t>PES</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -539,7 +539,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Gabriela Sampaio</t>
+          <t>PPCC</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -551,7 +551,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Gil Lima</t>
+          <t>PPF</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -563,7 +563,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Gilmara Dantas</t>
+          <t>PSF</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -575,7 +575,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Juliana Menezes</t>
+          <t>CCI</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -587,7 +587,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Mickela Souza</t>
+          <t>GA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -599,7 +599,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Monique Bendahan</t>
+          <t>GAC</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -611,7 +611,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Rafael Sales</t>
+          <t>GOF</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -623,7 +623,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Rosa Anjos</t>
+          <t>JUR</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -635,7 +635,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Silvana Souza</t>
+          <t>KFW-PFP</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -647,7 +647,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Silvio Rocha</t>
+          <t>KFW-REM</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -659,7 +659,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Thiago Carvalho</t>
+          <t>KFW-SBIO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -671,10 +671,46 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Wildney Mourão</t>
+          <t>PGT</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
+        <is>
+          <t>08:00,18:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>RH</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>08:00,18:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>TI</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>08:00,18:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>GFP e KFW</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
         <is>
           <t>08:00,18:00</t>
         </is>
